--- a/N6-WS1/Bảng công việc.xlsx
+++ b/N6-WS1/Bảng công việc.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>Thành viên</t>
   </si>
@@ -75,76 +75,82 @@
     <t>ID</t>
   </si>
   <si>
-    <t>Mô tả công việc</t>
-  </si>
-  <si>
-    <t>Độ ưu tiên</t>
+    <t>As a/an (User role)</t>
+  </si>
+  <si>
+    <t>I want to (Goal)</t>
+  </si>
+  <si>
+    <t>So that (Reason)</t>
   </si>
   <si>
     <t>Priority</t>
   </si>
   <si>
-    <t>Người thực hiện</t>
+    <t>Business Value</t>
   </si>
   <si>
     <t>PB01</t>
   </si>
   <si>
-    <t>Thiết kế Database</t>
-  </si>
-  <si>
-    <t>Tạo bảng sản phẩm, hóa đơn, nhân viên, khách hàng</t>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Thiết kế cơ sở dữ liệu cho sản phẩm, hóa đơn, nhân viên và khách hàng</t>
+  </si>
+  <si>
+    <t>Tôi có thể lưu trữ và quản lý toàn bộ dữ liệu của hệ thống</t>
   </si>
   <si>
     <t>Cao</t>
   </si>
   <si>
-    <t>DEV</t>
-  </si>
-  <si>
     <t>PB02</t>
   </si>
   <si>
-    <t>Đăng nhập</t>
-  </si>
-  <si>
-    <t>Xây dựng chức năng đăng nhập</t>
+    <t>Đăng nhập vào hệ thống</t>
+  </si>
+  <si>
+    <t>Tôi có thể truy cập và sử dụng hệ thống một cách bảo mật</t>
   </si>
   <si>
     <t>PB03</t>
   </si>
   <si>
-    <t>Quản lý nhân viên</t>
-  </si>
-  <si>
-    <t>CRUD nhân viên</t>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Quản lý nhân viên (thêm, sửa, xóa)</t>
+  </si>
+  <si>
+    <t>Tôi có thể kiểm soát thông tin nhân viên trong cửa hàng</t>
   </si>
   <si>
     <t>PB04</t>
   </si>
   <si>
-    <t>Quản lý sản phẩm</t>
-  </si>
-  <si>
-    <t>Thêm, sửa, xóa, tìm sản phẩm</t>
+    <t>Quản lý sản phẩm (thêm, sửa, xóa, tìm kiếm)</t>
+  </si>
+  <si>
+    <t>Tôi có thể quản lý danh sách laptop bán trong cửa hàng</t>
   </si>
   <si>
     <t>PB05</t>
   </si>
   <si>
-    <t>Quản lý cấu hình laptop</t>
-  </si>
-  <si>
-    <t>CPU, RAM, GPU, SSD, Seri</t>
+    <t>Quản lý cấu hình laptop (CPU, RAM, GPU, SSD, Seri)</t>
+  </si>
+  <si>
+    <t>Tôi có thể quản lý chi tiết cấu hình của từng laptop</t>
   </si>
   <si>
     <t>PB06</t>
   </si>
   <si>
-    <t>Tìm kiếm sản phẩm</t>
-  </si>
-  <si>
-    <t>Tìm theo tên hoặc mã</t>
+    <t>Tìm kiếm sản phẩm theo tên hoặc mã</t>
+  </si>
+  <si>
+    <t>Tôi có thể tìm laptop nhanh chóng</t>
   </si>
   <si>
     <t>Trung bình</t>
@@ -153,64 +159,67 @@
     <t>PB07</t>
   </si>
   <si>
-    <t>Tạo hóa đơn</t>
+    <t>Sales Staff</t>
   </si>
   <si>
     <t>Tạo hóa đơn bán hàng</t>
   </si>
   <si>
+    <t>Tôi có thể ghi nhận giao dịch bán laptop cho khách hàng</t>
+  </si>
+  <si>
     <t>PB08</t>
   </si>
   <si>
-    <t>Giỏ hàng</t>
-  </si>
-  <si>
-    <t>Thêm, sửa, xóa sản phẩm</t>
+    <t>Thêm, sửa, xóa sản phẩm trong giỏ hàng</t>
+  </si>
+  <si>
+    <t>Tôi có thể chuẩn bị đơn hàng trước khi thanh toán</t>
   </si>
   <si>
     <t>PB09</t>
   </si>
   <si>
-    <t>Thanh toán</t>
-  </si>
-  <si>
     <t>Chọn hình thức thanh toán</t>
   </si>
   <si>
+    <t>Tôi có thể hoàn tất giao dịch bán hàng</t>
+  </si>
+  <si>
     <t>PB10</t>
   </si>
   <si>
-    <t>Quản lý khách hàng</t>
-  </si>
-  <si>
-    <t>CRUD khách hàng</t>
+    <t>Quản lý thông tin khách hàng</t>
+  </si>
+  <si>
+    <t>Tôi có thể lưu trữ và theo dõi lịch sử mua hàng của khách</t>
   </si>
   <si>
     <t>PB11</t>
   </si>
   <si>
-    <t>Quản lý khuyến mãi</t>
-  </si>
-  <si>
-    <t>Tạo và áp dụng khuyến mãi</t>
+    <t>Quản lý khuyến mãi và voucher</t>
+  </si>
+  <si>
+    <t>Tôi có thể áp dụng giảm giá cho đơn hàng của khách</t>
   </si>
   <si>
     <t>PB12</t>
   </si>
   <si>
-    <t>Quản lý hóa đơn</t>
-  </si>
-  <si>
-    <t>Xem và tìm hóa đơn</t>
+    <t>Xem và tìm kiếm hóa đơn</t>
+  </si>
+  <si>
+    <t>Tôi có thể kiểm tra lại các giao dịch đã bán</t>
   </si>
   <si>
     <t>PB13</t>
   </si>
   <si>
-    <t>Thống kê doanh thu</t>
-  </si>
-  <si>
-    <t>Theo ngày, tháng, năm</t>
+    <t>Xem thống kê doanh thu theo ngày, tháng, năm</t>
+  </si>
+  <si>
+    <t>Tôi có thể đánh giá tình hình kinh doanh</t>
   </si>
   <si>
     <t>Thấp</t>
@@ -219,19 +228,19 @@
     <t>PB14</t>
   </si>
   <si>
-    <t>Biểu đồ thống kê</t>
-  </si>
-  <si>
-    <t>Hiển thị biểu đồ doanh thu</t>
+    <t>Xem biểu đồ doanh thu</t>
+  </si>
+  <si>
+    <t>Tôi có thể dễ dàng phân tích dữ liệu bán hàng</t>
   </si>
   <si>
     <t>PB15</t>
   </si>
   <si>
-    <t>Đăng xuất</t>
-  </si>
-  <si>
-    <t>Thoát hệ thống</t>
+    <t>Đăng xuất khỏi hệ thống</t>
+  </si>
+  <si>
+    <t>Tôi có thể thoát hệ thống một cách an toàn</t>
   </si>
 </sst>
 </file>
@@ -244,13 +253,34 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman Regular"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
@@ -259,12 +289,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -409,7 +433,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,7 +442,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,12 +611,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,162 +802,165 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1484,57 +1505,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.75" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="47.75" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="24.75" spans="1:3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="24.75" spans="1:3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" ht="24.75" spans="1:3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1550,9 +1571,9 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="27.203125" customWidth="1"/>
+    <col min="2" max="2" width="11.5859375" customWidth="1"/>
     <col min="3" max="3" width="54.546875" customWidth="1"/>
-    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="38.0234375" customWidth="1"/>
     <col min="5" max="5" width="21.3515625" customWidth="1"/>
     <col min="6" max="6" width="19.78125" customWidth="1"/>
   </cols>
@@ -1562,323 +1583,323 @@
         <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" ht="47" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="47" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="47" spans="1:6">
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="6">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" ht="24" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="F4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" ht="47" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="47" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" ht="47" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="C7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="47" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="6">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" ht="24" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="5">
+    </row>
+    <row r="9" ht="47" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="6">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" ht="24" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="F9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="47" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="47" spans="1:6">
+      <c r="A11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="5">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" ht="24" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="6">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" ht="24" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="24" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="C11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="7">
         <v>3</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" ht="24" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="5">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" ht="24" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="24" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="5">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" ht="24" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="6">
+    </row>
+    <row r="12" ht="47" spans="1:6">
+      <c r="A12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="7">
         <v>3</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" ht="24" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="F12" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" ht="47" spans="1:6">
+      <c r="A13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="7">
         <v>3</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" ht="24" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="6">
-        <v>3</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" ht="24" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="F13" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" ht="47" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="5">
+      <c r="B14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="6">
         <v>4</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" ht="24" spans="1:6">
-      <c r="A15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="5">
+    </row>
+    <row r="15" ht="47" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="6">
         <v>4</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" ht="24" spans="1:6">
-      <c r="A16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="F15" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" ht="47" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="6">
         <v>4</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>23</v>
+      <c r="F16" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="3:3">
-      <c r="C20" s="4"/>
+      <c r="C20" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
